--- a/outputs/evaluation/architecture/design/v1/CF_M01/run_3/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v1/CF_M01/run_3/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.3438</v>
       </c>
       <c r="D3" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9757</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.125</v>
       </c>
       <c r="D4" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8933</v>
       </c>
     </row>
@@ -1226,13 +1240,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -1256,13 +1268,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.8933</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_14</t>
@@ -1315,7 +1323,6 @@
           <t>capa de presentació, api gateway</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -1390,13 +1396,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1472,13 +1474,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -1502,13 +1502,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,13 +1552,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -1584,13 +1580,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1636,13 +1630,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -1666,13 +1658,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1718,13 +1708,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -1748,13 +1736,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU32</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1795,14 +1781,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Client</t>
@@ -1826,13 +1809,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1878,13 +1859,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -1908,13 +1887,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1960,13 +1937,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -1990,13 +1965,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2037,14 +2010,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Server</t>
@@ -2068,13 +2038,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2115,14 +2083,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -2141,14 +2106,11 @@
       <c r="P13" t="n">
         <v>41</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2222,7 +2184,6 @@
           <t>Capa de presentació</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>És la capa que s’encarrega de mostrar la informació a l’usuari.</t>
@@ -2258,7 +2219,6 @@
           <t>Capa de negoci</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Aquesta capa és el nucli de l’aplicació, que s’encarrega de processar tota la informació.</t>
@@ -2294,7 +2254,6 @@
           <t>Capa de dades</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>És la capa que s’encarrega d'emmagatzemar totes les dades.</t>
@@ -2330,7 +2289,6 @@
           <t>Mòdul analític</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>El mòdul analític té com a funció principal obtenir i processar les dades dels playlogs, les connexions i les accions en plataforma.</t>
@@ -2366,7 +2324,6 @@
           <t>3-layer architecture</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
@@ -2458,7 +2415,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
@@ -2489,7 +2445,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -2505,7 +2460,6 @@
           <t>AU_14</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.7856</v>
       </c>
@@ -2526,7 +2480,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -2537,7 +2490,6 @@
           <t>AU_14</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7402</v>
       </c>
@@ -2558,7 +2510,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -2594,7 +2545,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
@@ -2605,7 +2555,6 @@
           <t>AU_14</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0.7539</v>
       </c>
@@ -2626,7 +2575,6 @@
           <t>Business Layer</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
@@ -2662,7 +2610,6 @@
           <t>Data Layer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
@@ -2698,7 +2645,6 @@
           <t>Web platform interface</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -2734,7 +2680,6 @@
           <t>Waapiti Mobile Platform</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -2765,7 +2710,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -2781,7 +2725,6 @@
           <t>AU_14</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0.7823</v>
       </c>
@@ -2797,7 +2740,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>api gateway service, core service, analytical module</t>
@@ -2838,7 +2780,6 @@
           <t>TCP</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>communication between the Api Gateway service is via the TCP communication protocol</t>
@@ -2874,7 +2815,6 @@
           <t>Analytical module</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
@@ -2905,7 +2845,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>player, api player</t>
@@ -2941,7 +2880,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>player, web socket</t>
@@ -2982,7 +2920,6 @@
           <t>SQL database</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -3018,7 +2955,6 @@
           <t>AWS cloud services set</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
@@ -3054,7 +2990,6 @@
           <t>Amazon Athena</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
@@ -3090,7 +3025,6 @@
           <t>AWS Glue</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
@@ -3126,7 +3060,6 @@
           <t>Kinesis Data Streams</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
@@ -3162,7 +3095,6 @@
           <t>Kinesis Data Firehose</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
@@ -3198,7 +3130,6 @@
           <t>NestJS</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
@@ -3234,7 +3165,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
@@ -3270,7 +3200,6 @@
           <t>AWS RDS</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -3301,7 +3230,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>analytical module, aws cloud services set, sql database</t>
@@ -3337,7 +3265,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>core service, sql database, aws cloud services set</t>
@@ -3378,7 +3305,6 @@
           <t>Three Layers</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
@@ -3414,7 +3340,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
